--- a/sample_data/projects/env_007/engagement_workbook.xlsx
+++ b/sample_data/projects/env_007/engagement_workbook.xlsx
@@ -227,7 +227,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3810000" cy="2381250"/>
@@ -598,33 +598,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15/01/2024</t>
+          <t>03/01/2024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33.1</v>
+        <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>150.7</v>
+        <v>245.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>EXCEEDANCE</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Compliant</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -641,24 +641,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21/02/2024</t>
+          <t>26/02/2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>17.4</v>
       </c>
       <c r="F3" t="n">
-        <v>154.6</v>
+        <v>141.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -684,28 +684,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22/03/2024</t>
+          <t>24/03/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>S. Clark</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>28.8</v>
+        <v>17.4</v>
       </c>
       <c r="F4" t="n">
-        <v>161.1</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24/04/2024</t>
+          <t>23/04/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -737,18 +737,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P. Davis</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>80.8</v>
+        <v>88</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17/05/2024</t>
+          <t>22/05/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="F6" t="n">
-        <v>166.9</v>
+        <v>196.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13/06/2024</t>
+          <t>11/06/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -823,18 +823,18 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27.7</v>
+        <v>21.9</v>
       </c>
       <c r="F7" t="n">
-        <v>103.1</v>
+        <v>179.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>13/07/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -866,18 +866,18 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21.6</v>
+        <v>33.9</v>
       </c>
       <c r="F8" t="n">
-        <v>149.2</v>
+        <v>121.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10/08/2024</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -913,14 +913,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.7</v>
+        <v>25.3</v>
       </c>
       <c r="F9" t="n">
-        <v>141.7</v>
+        <v>157.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -942,24 +942,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24/09/2024</t>
+          <t>01/09/2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11.7</v>
+        <v>20.1</v>
       </c>
       <c r="F10" t="n">
-        <v>188.5</v>
+        <v>157.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -985,33 +985,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11/10/2024</t>
+          <t>26/10/2024</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30.8</v>
+        <v>15.5</v>
       </c>
       <c r="F11" t="n">
-        <v>178.6</v>
+        <v>206.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>EXCEEDANCE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Compliant</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10/11/2024</t>
+          <t>12/11/2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1042,14 +1042,14 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.4</v>
+        <v>29.6</v>
       </c>
       <c r="F12" t="n">
-        <v>192.4</v>
+        <v>176.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1085,14 +1085,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>34.5</v>
+        <v>20.4</v>
       </c>
       <c r="F13" t="n">
-        <v>197</v>
+        <v>127.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1114,33 +1114,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18/01/2024</t>
+          <t>19/01/2024</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P. Davis</t>
+          <t>S. Clark</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27.2</v>
+        <v>24.1</v>
       </c>
       <c r="F14" t="n">
-        <v>216.9</v>
+        <v>190</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18/02/2024</t>
+          <t>06/02/2024</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1167,23 +1167,23 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P. Davis</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>26.2</v>
+        <v>17.5</v>
       </c>
       <c r="F15" t="n">
-        <v>240.9</v>
+        <v>162.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1200,24 +1200,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01/03/2024</t>
+          <t>08/03/2024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Barnard Castle UK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>29.8</v>
+        <v>26.1</v>
       </c>
       <c r="F16" t="n">
-        <v>174.1</v>
+        <v>136.4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1243,24 +1243,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09/04/2024</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.4</v>
+        <v>12.9</v>
       </c>
       <c r="F17" t="n">
-        <v>90.2</v>
+        <v>204.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1286,28 +1286,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>02/05/2024</t>
+          <t>14/05/2024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>26.5</v>
+        <v>24.1</v>
       </c>
       <c r="F18" t="n">
-        <v>106.4</v>
+        <v>183.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1329,24 +1329,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27/06/2024</t>
+          <t>21/06/2024</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>28.3</v>
+        <v>25.2</v>
       </c>
       <c r="F19" t="n">
-        <v>85.8</v>
+        <v>204.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1372,24 +1372,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18/07/2024</t>
+          <t>11/07/2024</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P. Davis</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>24.6</v>
+        <v>21.2</v>
       </c>
       <c r="F20" t="n">
-        <v>201.6</v>
+        <v>105.3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1415,28 +1415,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26/08/2024</t>
+          <t>16/08/2024</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14.4</v>
+        <v>31.4</v>
       </c>
       <c r="F21" t="n">
-        <v>221.2</v>
+        <v>251.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1458,24 +1458,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>17/09/2024</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F22" t="n">
-        <v>149.8</v>
+        <v>253.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20/10/2024</t>
+          <t>27/10/2024</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1511,18 +1511,18 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8.4</v>
+        <v>26.5</v>
       </c>
       <c r="F23" t="n">
-        <v>125.2</v>
+        <v>154.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1544,33 +1544,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21/11/2024</t>
+          <t>26/11/2024</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>S. Clark</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>32.6</v>
+        <v>12.5</v>
       </c>
       <c r="F24" t="n">
-        <v>206.8</v>
+        <v>181.8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1592,28 +1592,28 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>8.9</v>
       </c>
       <c r="F25" t="n">
-        <v>253.6</v>
+        <v>120.5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>06/01/2024</t>
+          <t>16/01/2024</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1644,19 +1644,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>34.6</v>
+        <v>23.3</v>
       </c>
       <c r="F26" t="n">
-        <v>93.40000000000001</v>
+        <v>219.1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>EXCEEDANCE</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Compliant</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1683,14 +1683,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>18.2</v>
+        <v>23.5</v>
       </c>
       <c r="F27" t="n">
-        <v>157.1</v>
+        <v>128.2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1716,33 +1716,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01/03/2024</t>
+          <t>07/03/2024</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P. Davis</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12.3</v>
+        <v>28.5</v>
       </c>
       <c r="F28" t="n">
-        <v>232.3</v>
+        <v>159.4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>08/04/2024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="F29" t="n">
-        <v>107.9</v>
+        <v>197.7</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1816,14 +1816,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>28.9</v>
+        <v>20.1</v>
       </c>
       <c r="F30" t="n">
-        <v>192.6</v>
+        <v>142.7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>03/06/2024</t>
+          <t>26/06/2024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29.3</v>
+        <v>31.4</v>
       </c>
       <c r="F31" t="n">
-        <v>179</v>
+        <v>101.1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26/07/2024</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33.8</v>
+        <v>29.9</v>
       </c>
       <c r="F32" t="n">
-        <v>173.7</v>
+        <v>185.8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1931,24 +1931,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>03/08/2024</t>
+          <t>07/08/2024</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>19.2</v>
+        <v>12.5</v>
       </c>
       <c r="F33" t="n">
-        <v>176.7</v>
+        <v>105.1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1974,28 +1974,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11/09/2024</t>
+          <t>20/09/2024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>31.9</v>
+        <v>23.4</v>
       </c>
       <c r="F34" t="n">
-        <v>199.4</v>
+        <v>175.8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2017,24 +2017,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17/10/2024</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>S. Clark</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="F35" t="n">
-        <v>215.5</v>
+        <v>206.7</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>08/11/2024</t>
+          <t>22/11/2024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2074,14 +2074,14 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>11.1</v>
+        <v>33.7</v>
       </c>
       <c r="F36" t="n">
-        <v>142.3</v>
+        <v>172.6</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Barnard Castle UK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="F37" t="n">
-        <v>202.9</v>
+        <v>221.4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2146,28 +2146,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/01/2024</t>
+          <t>05/01/2024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Barnard Castle UK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>18.4</v>
+        <v>26.9</v>
       </c>
       <c r="F38" t="n">
-        <v>177.2</v>
+        <v>103.9</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2203,19 +2203,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>21.9</v>
+        <v>28.6</v>
       </c>
       <c r="F39" t="n">
-        <v>171.6</v>
+        <v>201.7</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17/03/2024</t>
+          <t>03/03/2024</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2242,18 +2242,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>32.3</v>
+        <v>25</v>
       </c>
       <c r="F40" t="n">
-        <v>114.7</v>
+        <v>147.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2275,24 +2275,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18/04/2024</t>
+          <t>12/04/2024</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12.5</v>
+        <v>21.9</v>
       </c>
       <c r="F41" t="n">
-        <v>252.1</v>
+        <v>130.1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21/05/2024</t>
+          <t>25/05/2024</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>24.9</v>
+        <v>16.8</v>
       </c>
       <c r="F42" t="n">
-        <v>117.9</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2361,24 +2361,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>27/06/2024</t>
+          <t>28/06/2024</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>30.6</v>
+        <v>25.1</v>
       </c>
       <c r="F43" t="n">
-        <v>117</v>
+        <v>205.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2404,28 +2404,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15/07/2024</t>
+          <t>07/07/2024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>S. Clark</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>28.2</v>
+        <v>13.9</v>
       </c>
       <c r="F44" t="n">
-        <v>107.7</v>
+        <v>157.3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2447,24 +2447,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>26/08/2024</t>
+          <t>18/08/2024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10.4</v>
+        <v>16.7</v>
       </c>
       <c r="F45" t="n">
-        <v>89.8</v>
+        <v>131</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2490,24 +2490,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>09/09/2024</t>
+          <t>11/09/2024</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P. Davis</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="F46" t="n">
-        <v>121</v>
+        <v>167.4</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11/10/2024</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P. Davis</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>20.2</v>
+        <v>10.7</v>
       </c>
       <c r="F47" t="n">
-        <v>152.8</v>
+        <v>221.1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2576,24 +2576,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21/11/2024</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>26.2</v>
+        <v>33.1</v>
       </c>
       <c r="F48" t="n">
-        <v>176.3</v>
+        <v>108.4</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2619,33 +2619,33 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23/12/2024</t>
+          <t>05/12/2024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Barnard Castle UK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>28.4</v>
+        <v>13.5</v>
       </c>
       <c r="F49" t="n">
-        <v>185.4</v>
+        <v>203.9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>EXCEEDANCE</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Compliant</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>26/01/2024</t>
+          <t>03/01/2024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2672,14 +2672,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>S. Clark</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>33.1</v>
+        <v>31.6</v>
       </c>
       <c r="F50" t="n">
-        <v>99.09999999999999</v>
+        <v>237.8</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13/02/2024</t>
+          <t>21/02/2024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>15.6</v>
+        <v>10.2</v>
       </c>
       <c r="F51" t="n">
-        <v>246.8</v>
+        <v>199.6</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2748,24 +2748,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>23/03/2024</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>20.8</v>
+        <v>18.7</v>
       </c>
       <c r="F52" t="n">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2791,24 +2791,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22/04/2024</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>J. Adams</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>33.9</v>
+        <v>25.7</v>
       </c>
       <c r="F53" t="n">
-        <v>105.9</v>
+        <v>206.7</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>04/05/2024</t>
+          <t>17/05/2024</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>22.9</v>
+        <v>10.1</v>
       </c>
       <c r="F54" t="n">
-        <v>179.9</v>
+        <v>186.9</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2877,24 +2877,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18/06/2024</t>
+          <t>04/06/2024</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>23.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>150.9</v>
+        <v>141.8</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2920,24 +2920,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>24/07/2024</t>
+          <t>03/07/2024</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>M. Brown</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="F56" t="n">
-        <v>213.5</v>
+        <v>121.2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17/08/2024</t>
+          <t>05/08/2024</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>19.1</v>
+        <v>16.5</v>
       </c>
       <c r="F57" t="n">
-        <v>196.3</v>
+        <v>238.6</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>09/09/2024</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3020,19 +3020,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>13</v>
+        <v>25.3</v>
       </c>
       <c r="F58" t="n">
-        <v>191</v>
+        <v>201.9</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3049,24 +3049,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>28/10/2024</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>P. Davis</t>
+          <t>M. Brown</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>12.9</v>
+        <v>24.5</v>
       </c>
       <c r="F59" t="n">
-        <v>223.9</v>
+        <v>109.5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3092,24 +3092,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22/11/2024</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>J. Adams</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>25.4</v>
+        <v>32.8</v>
       </c>
       <c r="F60" t="n">
-        <v>93.2</v>
+        <v>190.9</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3135,33 +3135,33 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16/12/2024</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>S. Clark</t>
+          <t>P. Davis</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10.7</v>
+        <v>32.2</v>
       </c>
       <c r="F61" t="n">
-        <v>210.6</v>
+        <v>105.2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>EXCEEDANCE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>EXCEEDANCE</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3189,7 +3189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -3268,23 +3268,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INS-2024-009</t>
+          <t>INS-2024-023</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="n">
-        <v>188.5</v>
+        <v>181.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INS-2024-043</t>
+          <t>INS-2024-028</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="E9" t="n">
-        <v>107.7</v>
+        <v>197.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INS-2024-042</t>
+          <t>INS-2024-021</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>117</v>
+        <v>253.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INS-2024-016</t>
+          <t>INS-2024-051</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9.4</v>
+        <v>18.7</v>
       </c>
       <c r="E11" t="n">
-        <v>90.2</v>
+        <v>135</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INS-2024-007</t>
+          <t>INS-2024-009</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3381,402 +3381,12 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="E12" t="n">
-        <v>149.2</v>
+        <v>157.3</v>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>INS-2024-019</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ware UK</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>201.6</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>INS-2024-040</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Montrose UK</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>252.1</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INS-2024-005</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ware UK</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>166.9</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>INS-2024-013</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Worthing UK</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>216.9</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>INS-2024-021</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Barnard Castle UK</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>33</v>
-      </c>
-      <c r="E17" t="n">
-        <v>149.8</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>INS-2024-032</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Barnard Castle UK</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>176.7</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>INS-2024-029</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Barnard Castle UK</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E19" t="n">
-        <v>192.6</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>INS-2024-022</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Worthing UK</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>125.2</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>INS-2024-054</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Stevenage UK</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>150.9</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>INS-2024-059</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Stevenage UK</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E22" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>INS-2024-020</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Barnard Castle UK</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E23" t="n">
-        <v>221.2</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>INS-2024-038</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Stevenage UK</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>171.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>18</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>INS-2024-010</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Montrose UK</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>178.6</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>19</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>INS-2024-037</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Stevenage UK</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E26" t="n">
-        <v>177.2</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>INS-2024-058</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Stevenage UK</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>223.9</v>
-      </c>
-      <c r="F27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3884,7 +3494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3949,12 +3559,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PM2.5 exceedance</t>
+          <t>NOx exceedance</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3986,12 +3596,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INS-2024-003</t>
+          <t>INS-2024-005</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4006,7 +3616,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15/04/2024</t>
+          <t>15/06/2024</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4028,12 +3638,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INS-2024-004</t>
+          <t>INS-2024-007</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4048,7 +3658,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15/05/2024</t>
+          <t>15/08/2024</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4070,12 +3680,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INS-2024-005</t>
+          <t>INS-2024-008</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4090,7 +3700,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15/06/2024</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4112,17 +3722,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INS-2024-006</t>
+          <t>INS-2024-010</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PM2.5 exceedance</t>
+          <t>NOx exceedance</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4132,7 +3742,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15/07/2024</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4154,12 +3764,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INS-2024-010</t>
+          <t>INS-2024-011</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Barnard Castle UK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4174,7 +3784,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>15/12/2024</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4196,12 +3806,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INS-2024-012</t>
+          <t>INS-2024-015</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Barnard Castle UK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4216,7 +3826,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15/12/2024</t>
+          <t>15/04/2024</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4238,7 +3848,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INS-2024-013</t>
+          <t>INS-2024-016</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4248,7 +3858,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PM2.5 exceedance</t>
+          <t>NOx exceedance</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4258,7 +3868,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15/02/2024</t>
+          <t>15/05/2024</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4280,12 +3890,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INS-2024-014</t>
+          <t>INS-2024-018</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4300,7 +3910,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15/03/2024</t>
+          <t>15/07/2024</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4322,12 +3932,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INS-2024-015</t>
+          <t>INS-2024-020</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4342,7 +3952,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15/04/2024</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4364,12 +3974,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INS-2024-017</t>
+          <t>INS-2024-021</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4384,7 +3994,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15/06/2024</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4406,7 +4016,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INS-2024-018</t>
+          <t>INS-2024-022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4426,7 +4036,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15/07/2024</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4448,12 +4058,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INS-2024-019</t>
+          <t>INS-2024-025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ware UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4468,7 +4078,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15/08/2024</t>
+          <t>15/02/2024</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4490,17 +4100,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INS-2024-020</t>
+          <t>INS-2024-027</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Worthing UK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NOx exceedance</t>
+          <t>PM2.5 exceedance</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4510,7 +4120,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>15/04/2024</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4532,7 +4142,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INS-2024-021</t>
+          <t>INS-2024-028</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4552,7 +4162,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>15/05/2024</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4574,12 +4184,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INS-2024-023</t>
+          <t>INS-2024-030</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4594,7 +4204,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15/12/2024</t>
+          <t>15/07/2024</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4616,12 +4226,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>INS-2024-024</t>
+          <t>INS-2024-031</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4636,7 +4246,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15/12/2024</t>
+          <t>15/08/2024</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4658,7 +4268,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INS-2024-025</t>
+          <t>INS-2024-034</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4668,7 +4278,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PM2.5 exceedance</t>
+          <t>NOx exceedance</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4678,7 +4288,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15/02/2024</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4700,17 +4310,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INS-2024-027</t>
+          <t>INS-2024-035</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NOx exceedance</t>
+          <t>PM2.5 exceedance</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4720,7 +4330,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15/04/2024</t>
+          <t>15/12/2024</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4742,7 +4352,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>INS-2024-028</t>
+          <t>INS-2024-036</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4762,7 +4372,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>15/05/2024</t>
+          <t>15/12/2024</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4784,7 +4394,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>INS-2024-029</t>
+          <t>INS-2024-037</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4804,7 +4414,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>15/06/2024</t>
+          <t>15/02/2024</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4826,12 +4436,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>INS-2024-030</t>
+          <t>INS-2024-038</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4846,7 +4456,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>15/07/2024</t>
+          <t>15/03/2024</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4868,12 +4478,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INS-2024-031</t>
+          <t>INS-2024-042</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4888,7 +4498,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15/08/2024</t>
+          <t>15/07/2024</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4910,17 +4520,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INS-2024-033</t>
+          <t>INS-2024-046</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PM2.5 exceedance</t>
+          <t>NOx exceedance</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4930,7 +4540,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4952,17 +4562,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INS-2024-034</t>
+          <t>INS-2024-047</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Stevenage UK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NOx exceedance</t>
+          <t>PM2.5 exceedance</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4972,7 +4582,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>15/12/2024</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4994,17 +4604,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INS-2024-036</t>
+          <t>INS-2024-048</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Worthing UK</t>
+          <t>Barnard Castle UK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PM2.5 exceedance</t>
+          <t>NOx exceedance</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5036,12 +4646,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INS-2024-039</t>
+          <t>INS-2024-049</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Barnard Castle UK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5056,7 +4666,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15/04/2024</t>
+          <t>15/02/2024</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5078,17 +4688,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INS-2024-040</t>
+          <t>INS-2024-052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NOx exceedance</t>
+          <t>PM2.5 exceedance</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5120,7 +4730,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>INS-2024-042</t>
+          <t>INS-2024-056</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5130,7 +4740,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PM2.5 exceedance</t>
+          <t>NOx exceedance</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5140,7 +4750,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15/07/2024</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5162,12 +4772,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INS-2024-043</t>
+          <t>INS-2024-057</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Barnard Castle UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5182,7 +4792,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>15/08/2024</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5204,12 +4814,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INS-2024-047</t>
+          <t>INS-2024-059</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Montrose UK</t>
+          <t>Ware UK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5246,12 +4856,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>INS-2024-048</t>
+          <t>INS-2024-060</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stevenage UK</t>
+          <t>Montrose UK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5275,300 +4885,6 @@
         </is>
       </c>
       <c r="H35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CA-2024-033</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>INS-2024-049</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Barnard Castle UK</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>PM2.5 exceedance</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Filter replacement</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>15/02/2024</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>CA-2024-034</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>INS-2024-050</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Worthing UK</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NOx exceedance</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Stack recalibration</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>15/03/2024</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CA-2024-035</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>INS-2024-052</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Barnard Castle UK</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>PM2.5 exceedance</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Filter replacement</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>15/05/2024</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CA-2024-036</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>INS-2024-055</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Barnard Castle UK</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NOx exceedance</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Stack recalibration</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>15/08/2024</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CA-2024-037</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>INS-2024-058</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Stevenage UK</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NOx exceedance</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Filter replacement</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>15/11/2024</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CA-2024-038</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>INS-2024-059</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Stevenage UK</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>PM2.5 exceedance</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Stack recalibration</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>15/12/2024</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CA-2024-039</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>INS-2024-060</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Barnard Castle UK</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NOx exceedance</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Filter replacement</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>15/12/2024</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
